--- a/intake_forms/026_patient_symptom_intake_form--intake_forms.xlsx
+++ b/intake_forms/026_patient_symptom_intake_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>joint_pain</t>
+          <t>joint pain</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>muscle_pain</t>
+          <t>muscle pain</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>shortness of breath</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>sore throat</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>loss_of_appetite</t>
+          <t>loss of appetite</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>loss_of_consciousness</t>
+          <t>loss of consciousness</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>numbness_or_weakness</t>
+          <t>numbness or weakness</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>loss_of_balance</t>
+          <t>loss of balance</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>speech_difficulty</t>
+          <t>speech difficulty</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>blurred_vision</t>
+          <t>blurred vision</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>double_vision</t>
+          <t>double vision</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>eye_redness</t>
+          <t>eye redness</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>eye_pain</t>
+          <t>eye pain</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>eye_discharge</t>
+          <t>eye discharge</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>yellowed_skin</t>
+          <t>yellowed skin</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>yellowed_eyes</t>
+          <t>yellowed eyes</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>swollen_lips</t>
+          <t>swollen lips</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>swollen_face</t>
+          <t>swollen face</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>swollen_joints</t>
+          <t>swollen joints</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sore_tongue</t>
+          <t>sore tongue</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bad_taste</t>
+          <t>bad taste</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>bad_smell</t>
+          <t>bad smell</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>runny_nose</t>
+          <t>runny nose</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>loss_of_taste</t>
+          <t>loss of taste</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>heart_burn</t>
+          <t>heart burn</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>chest_pain</t>
+          <t>chest pain</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>heart_palpitations</t>
+          <t>heart palpitations</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>chest_pains</t>
+          <t>chest pains</t>
         </is>
       </c>
     </row>
